--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-LETTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C7BD30-62A2-4C7F-A288-62037784E367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280ADB59-FFCF-47D7-8DCD-7F3EEB34691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6345" yWindow="3645" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team List" sheetId="3" r:id="rId1"/>
@@ -206,13 +206,13 @@
     <t>${t.get("Gender.Women")}</t>
   </si>
   <si>
-    <t>${masters ? l.mastersLongRegistrationCategoryName : l.registrationCategory}</t>
-  </si>
-  <si>
     <t>VFE</t>
   </si>
   <si>
     <t>${t.get("Jury.Signature")}</t>
+  </si>
+  <si>
+    <t>${l.categoryName}</t>
   </si>
 </sst>
 </file>
@@ -525,6 +525,29 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -537,29 +560,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,16 +1007,16 @@
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
       <c r="L2" s="4"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -1037,14 +1037,14 @@
         <v>4</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
       <c r="L3" s="4"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -1065,14 +1065,14 @@
         <v>7</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
       <c r="L4" s="4"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -1083,18 +1083,18 @@
       <c r="X4"/>
     </row>
     <row r="5" spans="1:24" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
+      <c r="A5" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
       <c r="K5" s="10"/>
       <c r="L5" s="11"/>
       <c r="M5" s="12"/>
@@ -1120,31 +1120,31 @@
       <c r="K6" s="18"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="1:24" s="48" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="42" t="s">
+    <row r="7" spans="1:24" s="43" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
     </row>
     <row r="8" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
@@ -1229,7 +1229,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G11" s="33"/>
       <c r="H11" s="33" t="s">
@@ -1297,7 +1297,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G14" s="33"/>
       <c r="H14" s="33" t="s">
@@ -1331,11 +1331,11 @@
       <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:24" s="20" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
+      <c r="A16" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="35"/>
       <c r="E16" s="36"/>
       <c r="F16" s="17"/>
@@ -2615,12 +2615,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="K10 K6 K11:K12" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-LETTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280ADB59-FFCF-47D7-8DCD-7F3EEB34691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577AA9D6-8D48-4B96-894F-4F278B915B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6345" yWindow="3645" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,6 @@
     <definedName name="P_C_">#REF!</definedName>
     <definedName name="PeséeGroupFilter">#REF!</definedName>
     <definedName name="PRÉNOM">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Team List'!$A:$F</definedName>
     <definedName name="progr_">#REF!</definedName>
     <definedName name="requestedCJ">#REF!</definedName>
     <definedName name="StartGroupFilter">#REF!</definedName>
@@ -943,8 +942,8 @@
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="11.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.28515625" style="3" customWidth="1"/>
     <col min="12" max="13" width="7.7109375" style="1" customWidth="1"/>
@@ -2629,7 +2628,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="53" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
